--- a/光伏配储项目/电价数据/2026/荷城站.xlsx
+++ b/光伏配储项目/电价数据/2026/荷城站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51066</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.78383</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.58778</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.61338</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52034</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5135</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43752</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44104</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42328</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44405</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.24056</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12779</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10374</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11788</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10614</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13007</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.08016</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.15194</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.14649</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.01485</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.12262</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.18029</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.22809</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.19274</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23875</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.08764</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00747</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.14613</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.20784</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20731</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.70928</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.50466</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.56535</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.31822</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.4264</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.47601</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57961</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6365599999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8241499999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64803</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.64613</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7956599999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.14238</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.44541</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68945</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5867</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.8114</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6065900000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65252</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.62439</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47833</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47775</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42562</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70775</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.54566</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7588200000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.34634</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8059400000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52849</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5187999999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5107200000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59727</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.70087</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42981</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43181</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5224099999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.22168</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06634999999999999</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.47883</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.48044</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.46521</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.48252</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.47476</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5230499999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7405</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.28185</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.6027</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.02461</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.52255</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.44042</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.48451</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5167</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.4753</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.44141</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.43403</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.62219</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7559600000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.6154400000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.7036399999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7659900000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7391</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.63149</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.5672</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.75742</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.5752</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.54702</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.00547</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.47121</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.5789800000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.68263</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.47078</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.48273</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.44234</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33455</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51266</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.86765</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.7340399999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.56616</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.46394</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.48381</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47381</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.48266</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4768</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.14023</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.78085</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.8222999999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21799</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.32514</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26794</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47968</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5267999999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.4919</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42885</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17004</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42931</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.52234</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43272</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.63878</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.71009</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.49646</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42551</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.52698</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42524</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.47703</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47255</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45859</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41689</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41789</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34241</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45897</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22899</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.25779</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.48167</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.5007699999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.57131</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48041</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.59946</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.48367</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.14763</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.09629</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.44728</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.26194</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.7674500000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07218000000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.19858</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.26208</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.26644</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24829</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21898</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13192</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.43002</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6134400000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46848</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44978</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29968</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.11958</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.11715</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.13152</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04457</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04573</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.08247</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03445</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04838</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04274</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04238</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04242</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04251</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04254</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.0454</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04497</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04187</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04169</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.0431</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04524</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2185</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04515</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05124</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05595</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.03591</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02009</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.22837</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.13261</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.17508</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35085</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.75897</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44612</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10316</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00197</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04461</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04353</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04313</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04324</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04516</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04406</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04448</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04954</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04725</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04763000000000001</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14299</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33565</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3179</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17257</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17112</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14786</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15959</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15876</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23642</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21418</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22673</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27184</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4546</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15637</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909400000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78107</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9205099999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91608</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86788</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29933</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89288</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6326499999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19241</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8714500000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54511</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33625</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03666</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53613</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7954600000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53028</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77749</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78111</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8773300000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87621</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49735</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40533</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21244</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87905</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55115</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62726</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5396799999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4992799999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43814</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43378</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58649</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42771</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59599</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60237</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66848</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47338</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58162</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45241</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8819900000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6346499999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.94796</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.9300900000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86499</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44367</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.47445</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.63797</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35343</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92431</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47744</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49998</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16573</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26255</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19912</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19869</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43527</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44838</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42039</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5966</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89039</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.37767</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.17688</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7134199999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8088099999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66318</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59112</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45584</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50795</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44498</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.44242</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41914</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42793</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5079399999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43977</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45585</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42793</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4080299999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5052</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.53883</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.91298</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.49852</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.55455</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.19001</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.48884</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.61739</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26272</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57935</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46737</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.78996</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.47104</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43724</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42172</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32396</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.5289199999999999</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.48982</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.50348</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.47901</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.24567</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.25296</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.25674</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.17865</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.23839</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.17862</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.2348</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.22844</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.43775</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.4157</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.19229</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.21701</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.44522</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.47128</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.42597</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.42826</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.45262</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.48279</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.47156</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.64732</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40318</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44714</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44306</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44235</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44746</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34877</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54662</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47422</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27147</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26456</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20029</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2487</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24148</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28845</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25232</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27474</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24055</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.21576</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.15299</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.24674</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.17967</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.23775</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42069</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36128</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.53418</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43505</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44152</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45172</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.06536</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.41269</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.18692</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26093</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.46538</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45286</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70585</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5179</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26185</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28688</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.49006</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34953</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64425</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.79592</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44489</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46138</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34146</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26437</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14177</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.2007</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26159</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28079</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22329</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27604</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14493</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43846</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.70023</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5918</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.4344</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6824600000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46777</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40913</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47771</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35998</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49002</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47696</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48444</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40889</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41078</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45486</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44844</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56531</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5069399999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45513</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.25103</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44553</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47721</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43265</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46534</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46728</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5811900000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.43127</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42174</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6499400000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.17177</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42255</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44287</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49895</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44282</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51962</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5032</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.44318</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.60853</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70382</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7044199999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8103899999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58353</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.51366</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.79788</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7404400000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6242799999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66115</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44334</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47827</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47734</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46056</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55128</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42981</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42668</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42166</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44194</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44955</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40435</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21326</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40466</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45954</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46354</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11724</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18075</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36531</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27939</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22738</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23071</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25056</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26554</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25379</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25121</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17085</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18334</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22905</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24995</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23252</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35004</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26525</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25147</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17205</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21364</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24646</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01839</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0009599999999999999</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02578</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11856</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03906</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03648</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03275</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04721</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02317</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.0224</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04914</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.15188</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00109</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04917</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04892000000000001</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03125</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04883</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0419</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18505</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20454</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24207</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27148</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26935</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27519</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.16163</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.6155900000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.18972</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.26089</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.25224</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27878</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26492</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23646</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26443</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25546</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27838</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28842</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24116</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.18646</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6742100000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.66855</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.68365</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.62476</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.18425</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11953</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24679</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.19912</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.14224</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14844</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.10781</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23368</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04422</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.12111</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04982</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18775</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02306</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.14161</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.15047</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.1649</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.00826</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.12425</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.1351</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.13394</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16865</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25874</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.44812</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32341</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.01801</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5605599999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.53386</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.43377</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.45422</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43884</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44622</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14174</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2788</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46234</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3273</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5731799999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.54626</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49589</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43695</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48235</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.49097</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45319</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46871</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.58335</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.46603</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.58863</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.42431</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.26045</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36427</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48114</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.41322</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41365</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.46431</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40422</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.49326</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43469</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5031100000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56948</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.57036</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.52842</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.53513</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.47348</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51989</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.47873</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.5518500000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55413</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5579</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.43236</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36943</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24249</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17052</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17776</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20732</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.03838</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21672</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17419</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26453</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16904</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06333</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05601</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07592</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17386</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.0837</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06075999999999999</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15841</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17795</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26239</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42085</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42566</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.25931</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36307</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8461799999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.4716</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43275</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38653</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26407</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11656</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01252</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01251</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.009640000000000001</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03879999999999999</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.16448</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03282</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00545</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01884</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04603</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02017</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.27969</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04548</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.24845</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.17293</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.26992</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48996</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5467799999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36408</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.57799</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26731</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23899</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14892</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21574</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23961</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24361</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15765</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.02533</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04718</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04721</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04572</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04625</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04454</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08119</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02859</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06445000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09995</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17899</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20599</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12568</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27098</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.24075</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12901</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.06001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26938</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.15424</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.12151</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24365</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19455</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.25064</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25585</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21249</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25476</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45982</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3733399999999999</v>
       </c>
     </row>
   </sheetData>
